--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$126</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="811">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:19:16+00:00</t>
+    <t>2026-08-06T13:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1284,6 +1284,214 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
   </si>
   <si>
+    <t>DocumentReference.securityLabel:confidentiality.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.system</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-Confidentiality</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.version</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.code</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.display</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality.text</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
     <t>DocumentReference.securityLabel:visibilityStatus</t>
   </si>
   <si>
@@ -1294,6 +1502,42 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.system</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.version</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.code</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.display</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus.text</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -2137,27 +2381,6 @@
     <t>DocumentReference.context.related.identifier.type.coding</t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.id</t>
   </si>
   <si>
@@ -2176,54 +2399,15 @@
     <t>DocumentReference.context.related.identifier.type.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
     <t>urn:ietf:rfc:3986</t>
   </si>
   <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.version</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.coding.version</t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.code</t>
   </si>
   <si>
@@ -2233,98 +2417,22 @@
     <t>[CXi.5] Identifier Type Code : urn:ihe:iti:xds:2016:studyInstanceUID | urn:ihe:iti:xds:2013:order | urn:ihe:iti:xds:2013:accession</t>
   </si>
   <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.display</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.userSelected</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.coding.userSelected</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.text</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.system</t>
@@ -2749,7 +2857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS104"/>
+  <dimension ref="A1:AS126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.97265625" customWidth="true" bestFit="true"/>
@@ -7950,16 +8058,14 @@
         <v>395</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C41" t="s" s="2">
         <v>405</v>
       </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7968,32 +8074,28 @@
         <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>406</v>
+        <v>112</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -8017,107 +8119,111 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>341</v>
+        <v>118</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>119</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -8154,22 +8260,22 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>125</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>84</v>
@@ -8178,7 +8284,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -8190,10 +8296,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>115</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8210,10 +8316,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8224,7 +8330,7 @@
         <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -8233,19 +8339,23 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>112</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -8293,19 +8403,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>114</v>
+        <v>414</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -8320,7 +8430,7 @@
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>115</v>
+        <v>415</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -8329,7 +8439,7 @@
         <v>82</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -8337,21 +8447,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -8363,17 +8473,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -8422,19 +8530,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -8466,14 +8574,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>352</v>
+        <v>117</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8486,26 +8594,24 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>118</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>119</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>120</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="O45" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -8541,19 +8647,19 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8580,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -8597,10 +8703,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8623,16 +8729,20 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -8641,7 +8751,7 @@
         <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>82</v>
@@ -8680,10 +8790,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>97</v>
@@ -8704,30 +8814,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8747,18 +8857,20 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>112</v>
+        <v>433</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8807,7 +8919,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>114</v>
+        <v>436</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8819,7 +8931,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8834,7 +8946,7 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>115</v>
+        <v>437</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8843,7 +8955,7 @@
         <v>82</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8851,21 +8963,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8874,21 +8986,21 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>119</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8924,31 +9036,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>125</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -8963,7 +9075,7 @@
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>115</v>
+        <v>269</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8972,7 +9084,7 @@
         <v>82</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -8980,10 +9092,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8991,7 +9103,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>97</v>
@@ -9006,17 +9118,17 @@
         <v>98</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9029,7 +9141,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9041,13 +9153,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9065,7 +9177,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9083,7 +9195,7 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
@@ -9092,7 +9204,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -9101,18 +9213,18 @@
         <v>82</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9120,13 +9232,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -9135,17 +9247,19 @@
         <v>98</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>175</v>
+        <v>456</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9158,7 +9272,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9170,13 +9284,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -9194,7 +9308,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9209,10 +9323,10 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -9221,7 +9335,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9230,7 +9344,7 @@
         <v>82</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -9238,10 +9352,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9252,7 +9366,7 @@
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -9261,22 +9375,22 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>447</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9325,7 +9439,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9352,7 +9466,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -9361,32 +9475,34 @@
         <v>82</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -9395,19 +9511,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>456</v>
+        <v>259</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>458</v>
+        <v>389</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>459</v>
+        <v>390</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>460</v>
+        <v>391</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9420,7 +9536,7 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>82</v>
@@ -9432,13 +9548,11 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -9456,54 +9570,54 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>387</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>463</v>
+        <v>109</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>465</v>
+        <v>395</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>466</v>
+        <v>397</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>467</v>
+        <v>399</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>405</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9511,7 +9625,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>97</v>
@@ -9523,23 +9637,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>469</v>
+        <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>112</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -9587,7 +9697,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>474</v>
+        <v>114</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9599,13 +9709,13 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>475</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
@@ -9614,7 +9724,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>476</v>
+        <v>115</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9631,21 +9741,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -9654,23 +9764,21 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>118</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>478</v>
+        <v>119</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>479</v>
+        <v>120</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -9706,37 +9814,37 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>482</v>
+        <v>125</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
@@ -9745,7 +9853,7 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>484</v>
+        <v>115</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9762,10 +9870,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>485</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9773,10 +9881,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9788,17 +9896,19 @@
         <v>98</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>486</v>
+        <v>410</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>488</v>
+        <v>413</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9811,7 +9921,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -9847,13 +9957,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>490</v>
+        <v>414</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9862,10 +9972,10 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
@@ -9874,7 +9984,7 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>493</v>
+        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9883,18 +9993,18 @@
         <v>82</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>494</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9902,33 +10012,31 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>495</v>
+        <v>111</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>496</v>
+        <v>112</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>497</v>
+        <v>113</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9976,7 +10084,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>499</v>
+        <v>114</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9988,13 +10096,13 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -10003,7 +10111,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>476</v>
+        <v>115</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -10018,44 +10126,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>481</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>503</v>
+        <v>119</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>504</v>
+        <v>120</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>505</v>
+        <v>121</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10081,59 +10189,61 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>125</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>507</v>
+        <v>126</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>412</v>
+        <v>115</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>82</v>
@@ -10142,15 +10252,15 @@
         <v>82</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10164,7 +10274,7 @@
         <v>97</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -10173,18 +10283,20 @@
         <v>98</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>341</v>
+        <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>513</v>
+        <v>423</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>424</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -10193,7 +10305,7 @@
         <v>82</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>82</v>
@@ -10232,7 +10344,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10259,7 +10371,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>516</v>
+        <v>429</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10268,7 +10380,7 @@
         <v>82</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="AS58" t="s" s="2">
         <v>82</v>
@@ -10276,10 +10388,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10299,18 +10411,20 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>112</v>
+        <v>433</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -10359,7 +10473,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>114</v>
+        <v>436</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10371,7 +10485,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -10386,7 +10500,7 @@
         <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>115</v>
+        <v>437</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -10395,7 +10509,7 @@
         <v>82</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -10403,21 +10517,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>518</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -10426,21 +10540,21 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>119</v>
+        <v>441</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -10488,19 +10602,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>125</v>
+        <v>444</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -10515,7 +10629,7 @@
         <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>115</v>
+        <v>269</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -10524,7 +10638,7 @@
         <v>82</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -10532,45 +10646,43 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>519</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>353</v>
+        <v>448</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>355</v>
+        <v>450</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -10619,19 +10731,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>356</v>
+        <v>451</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -10646,7 +10758,7 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>198</v>
+        <v>452</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -10655,7 +10767,7 @@
         <v>82</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AS61" t="s" s="2">
         <v>82</v>
@@ -10663,10 +10775,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>455</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10677,7 +10789,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -10686,19 +10798,23 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>522</v>
+        <v>457</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -10746,13 +10862,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>520</v>
+        <v>461</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -10764,25 +10880,25 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>527</v>
+        <v>462</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AS62" t="s" s="2">
         <v>82</v>
@@ -10790,10 +10906,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>529</v>
+        <v>465</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10804,7 +10920,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10813,21 +10929,23 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>530</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>531</v>
+        <v>467</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10851,13 +10969,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10875,34 +10993,34 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>529</v>
+        <v>470</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>535</v>
+        <v>109</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>539</v>
+        <v>471</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -10911,18 +11029,18 @@
         <v>82</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10945,13 +11063,13 @@
         <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>541</v>
+        <v>341</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>542</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>543</v>
+        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11002,13 +11120,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -11026,13 +11144,13 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>544</v>
+        <v>492</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>545</v>
+        <v>493</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>82</v>
@@ -11041,15 +11159,15 @@
         <v>82</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11173,10 +11291,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11246,16 +11364,16 @@
         <v>82</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>125</v>
@@ -11302,44 +11420,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>495</v>
+        <v>118</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>353</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>354</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -11387,25 +11507,25 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>554</v>
+        <v>356</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>557</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
@@ -11414,7 +11534,7 @@
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>558</v>
+        <v>198</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -11423,7 +11543,7 @@
         <v>82</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
       <c r="AS67" t="s" s="2">
         <v>82</v>
@@ -11431,10 +11551,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>560</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>560</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11442,7 +11562,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>97</v>
@@ -11457,24 +11577,20 @@
         <v>98</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>561</v>
+        <v>499</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q68" t="s" s="2">
-        <v>564</v>
-      </c>
+      <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
         <v>82</v>
       </c>
@@ -11518,54 +11634,54 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>565</v>
+        <v>497</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>568</v>
+        <v>493</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>569</v>
+        <v>503</v>
       </c>
       <c r="AS68" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>570</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>570</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11573,13 +11689,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -11588,13 +11704,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>571</v>
+        <v>112</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>572</v>
+        <v>113</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11621,11 +11737,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11643,7 +11761,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>570</v>
+        <v>114</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11655,25 +11773,25 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>574</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>578</v>
+        <v>115</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>579</v>
+        <v>82</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
@@ -11682,29 +11800,29 @@
         <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>580</v>
+        <v>506</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>580</v>
+        <v>506</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -11713,20 +11831,18 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>581</v>
+        <v>119</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>582</v>
+        <v>120</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11750,59 +11866,61 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>585</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>580</v>
+        <v>125</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>574</v>
+        <v>126</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>578</v>
+        <v>115</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11811,15 +11929,15 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>588</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>588</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11833,25 +11951,27 @@
         <v>97</v>
       </c>
       <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K71" t="s" s="2">
-        <v>589</v>
+        <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>590</v>
+        <v>508</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>591</v>
+        <v>509</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11863,7 +11983,7 @@
         <v>82</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>82</v>
@@ -11875,13 +11995,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -11899,7 +12019,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>588</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11917,36 +12037,36 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>295</v>
+        <v>516</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>593</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>593</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11954,31 +12074,33 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>113</v>
+        <v>520</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11990,7 +12112,7 @@
         <v>82</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>82</v>
@@ -12002,13 +12124,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -12026,7 +12148,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>114</v>
+        <v>523</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12038,13 +12160,13 @@
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>82</v>
@@ -12053,7 +12175,7 @@
         <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>115</v>
+        <v>526</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>82</v>
@@ -12070,21 +12192,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>594</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>594</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -12096,18 +12218,20 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>118</v>
+        <v>528</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>119</v>
+        <v>529</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>120</v>
+        <v>530</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -12143,31 +12267,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>125</v>
+        <v>533</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -12182,7 +12306,7 @@
         <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>115</v>
+        <v>534</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>82</v>
@@ -12191,7 +12315,7 @@
         <v>82</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>82</v>
@@ -12199,10 +12323,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>595</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>595</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12210,7 +12334,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>97</v>
@@ -12225,18 +12349,20 @@
         <v>98</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>537</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>596</v>
+        <v>538</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>597</v>
+        <v>539</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -12248,7 +12374,7 @@
         <v>82</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>82</v>
@@ -12284,7 +12410,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>599</v>
+        <v>543</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12293,16 +12419,16 @@
         <v>97</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>109</v>
+        <v>544</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>601</v>
+        <v>546</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12311,7 +12437,7 @@
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>198</v>
+        <v>547</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>82</v>
@@ -12320,7 +12446,7 @@
         <v>82</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AS74" t="s" s="2">
         <v>82</v>
@@ -12328,10 +12454,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>602</v>
+        <v>549</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>602</v>
+        <v>549</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12339,7 +12465,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>97</v>
@@ -12354,18 +12480,20 @@
         <v>98</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>140</v>
+        <v>550</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>603</v>
+        <v>551</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>604</v>
+        <v>552</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -12389,13 +12517,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -12413,7 +12541,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>608</v>
+        <v>555</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12431,7 +12559,7 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
@@ -12440,7 +12568,7 @@
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>198</v>
+        <v>557</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>82</v>
@@ -12457,10 +12585,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>609</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>609</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12468,7 +12596,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>97</v>
@@ -12483,18 +12611,20 @@
         <v>98</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>227</v>
+        <v>528</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>610</v>
+        <v>559</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>611</v>
+        <v>560</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -12542,7 +12672,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>613</v>
+        <v>563</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12560,7 +12690,7 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>614</v>
+        <v>564</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
@@ -12569,7 +12699,7 @@
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>615</v>
+        <v>565</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -12586,10 +12716,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>616</v>
+        <v>566</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>616</v>
+        <v>566</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12597,7 +12727,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>97</v>
@@ -12615,15 +12745,15 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>617</v>
+        <v>567</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -12635,7 +12765,7 @@
         <v>82</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>82</v>
+        <v>570</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>82</v>
@@ -12671,7 +12801,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>620</v>
+        <v>571</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12686,10 +12816,10 @@
         <v>109</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
@@ -12698,7 +12828,7 @@
         <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>198</v>
+        <v>574</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>82</v>
@@ -12713,12 +12843,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>621</v>
+        <v>575</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>621</v>
+        <v>575</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12726,10 +12856,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>98</v>
@@ -12738,21 +12868,21 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>622</v>
+        <v>576</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>623</v>
+        <v>577</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -12788,25 +12918,25 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>621</v>
+        <v>580</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -12815,22 +12945,22 @@
         <v>109</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>628</v>
+        <v>582</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>630</v>
+        <v>557</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>82</v>
@@ -12839,49 +12969,47 @@
         <v>82</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>632</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>633</v>
+        <v>583</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>634</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>622</v>
+        <v>153</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>635</v>
+        <v>584</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>624</v>
+        <v>585</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>625</v>
+        <v>586</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12907,13 +13035,11 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -12931,37 +13057,37 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>621</v>
+        <v>583</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>109</v>
+        <v>588</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>628</v>
+        <v>590</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>629</v>
+        <v>591</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>630</v>
+        <v>493</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>631</v>
+        <v>592</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>82</v>
@@ -12970,15 +13096,15 @@
         <v>82</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>632</v>
+        <v>590</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>636</v>
+        <v>593</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>637</v>
+        <v>593</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12986,30 +13112,32 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>111</v>
+        <v>341</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>112</v>
+        <v>594</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13058,7 +13186,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>114</v>
+        <v>593</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13070,7 +13198,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -13085,7 +13213,7 @@
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>115</v>
+        <v>597</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>82</v>
@@ -13102,21 +13230,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>638</v>
+        <v>598</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>639</v>
+        <v>598</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -13128,17 +13256,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -13175,31 +13301,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -13231,21 +13357,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>641</v>
+        <v>599</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -13254,19 +13380,19 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>596</v>
+        <v>119</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>597</v>
+        <v>120</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>598</v>
+        <v>121</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13316,19 +13442,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>599</v>
+        <v>125</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -13343,7 +13469,7 @@
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -13360,44 +13486,46 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>642</v>
+        <v>600</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>643</v>
+        <v>600</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>603</v>
+        <v>353</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>604</v>
+        <v>354</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -13421,13 +13549,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -13445,19 +13573,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>608</v>
+        <v>356</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -13487,12 +13615,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>644</v>
+        <v>601</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>645</v>
+        <v>601</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13503,29 +13631,27 @@
         <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>227</v>
+        <v>602</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -13574,13 +13700,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -13592,22 +13718,22 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>82</v>
@@ -13618,10 +13744,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>646</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13632,7 +13758,7 @@
         <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -13644,15 +13770,17 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>112</v>
+        <v>611</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -13677,13 +13805,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>82</v>
+        <v>615</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -13701,34 +13829,34 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>114</v>
+        <v>610</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>115</v>
+        <v>620</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>82</v>
@@ -13740,48 +13868,46 @@
         <v>82</v>
       </c>
       <c r="AS85" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>649</v>
+        <v>621</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>118</v>
+        <v>622</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>119</v>
+        <v>623</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -13818,31 +13944,31 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>125</v>
+        <v>621</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -13854,13 +13980,13 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>82</v>
+        <v>625</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>115</v>
+        <v>626</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>82</v>
@@ -13869,15 +13995,15 @@
         <v>82</v>
       </c>
       <c r="AS86" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13894,26 +14020,22 @@
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>652</v>
+        <v>112</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>655</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13937,13 +14059,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -13961,7 +14083,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>658</v>
+        <v>114</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13973,7 +14095,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13988,7 +14110,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>659</v>
+        <v>115</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -13997,7 +14119,7 @@
         <v>82</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AS87" t="s" s="2">
         <v>82</v>
@@ -14005,21 +14127,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>661</v>
+        <v>630</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -14028,23 +14150,21 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>662</v>
+        <v>119</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>663</v>
+        <v>120</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -14068,43 +14188,43 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>666</v>
+        <v>82</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>668</v>
+        <v>125</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -14119,7 +14239,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>659</v>
+        <v>115</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14128,7 +14248,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14136,10 +14256,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>670</v>
+        <v>631</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>671</v>
+        <v>631</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14147,7 +14267,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>97</v>
@@ -14159,18 +14279,20 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>576</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>112</v>
+        <v>632</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>634</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -14219,7 +14341,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>114</v>
+        <v>635</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14228,16 +14350,16 @@
         <v>97</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>82</v>
+        <v>636</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>82</v>
+        <v>638</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>82</v>
@@ -14246,7 +14368,7 @@
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>115</v>
+        <v>639</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>82</v>
@@ -14255,7 +14377,7 @@
         <v>82</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>82</v>
+        <v>640</v>
       </c>
       <c r="AS89" t="s" s="2">
         <v>82</v>
@@ -14263,21 +14385,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>672</v>
+        <v>641</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>673</v>
+        <v>641</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -14286,25 +14408,27 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>118</v>
+        <v>576</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>119</v>
+        <v>642</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>120</v>
+        <v>643</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>121</v>
+        <v>644</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>645</v>
+      </c>
       <c r="R90" t="s" s="2">
         <v>82</v>
       </c>
@@ -14336,37 +14460,37 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>125</v>
+        <v>646</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>636</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
@@ -14375,7 +14499,7 @@
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>115</v>
+        <v>649</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>82</v>
@@ -14384,18 +14508,18 @@
         <v>82</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="AS90" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14403,35 +14527,31 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>679</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -14455,13 +14575,11 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -14479,54 +14597,54 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>680</v>
+        <v>651</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>109</v>
+        <v>655</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>681</v>
+        <v>659</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>82</v>
+        <v>660</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>682</v>
+        <v>82</v>
       </c>
       <c r="AS91" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>683</v>
+        <v>661</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>684</v>
+        <v>661</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14534,13 +14652,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
@@ -14549,16 +14667,20 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>112</v>
+        <v>662</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -14582,13 +14704,11 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>666</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -14606,7 +14726,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>114</v>
+        <v>661</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14618,25 +14738,25 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>668</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>115</v>
+        <v>659</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>82</v>
@@ -14645,29 +14765,29 @@
         <v>82</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>82</v>
+        <v>668</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>82</v>
@@ -14676,17 +14796,15 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>118</v>
+        <v>670</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>119</v>
+        <v>671</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -14723,31 +14841,31 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>125</v>
+        <v>669</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -14759,13 +14877,13 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>82</v>
@@ -14774,15 +14892,15 @@
         <v>82</v>
       </c>
       <c r="AS93" t="s" s="2">
-        <v>82</v>
+        <v>673</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14802,23 +14920,19 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>689</v>
+        <v>112</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>692</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -14827,7 +14941,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>693</v>
+        <v>82</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14866,7 +14980,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>694</v>
+        <v>114</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14878,7 +14992,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -14893,7 +15007,7 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>695</v>
+        <v>115</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
@@ -14902,7 +15016,7 @@
         <v>82</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>696</v>
+        <v>82</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14910,21 +15024,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>698</v>
+        <v>675</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -14933,19 +15047,19 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>699</v>
+        <v>119</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>701</v>
+        <v>121</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14983,31 +15097,31 @@
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>702</v>
+        <v>125</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -15022,7 +15136,7 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>703</v>
+        <v>115</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>82</v>
@@ -15031,18 +15145,18 @@
         <v>82</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>704</v>
+        <v>82</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>705</v>
+        <v>676</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>706</v>
+        <v>676</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15056,7 +15170,7 @@
         <v>97</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -15065,18 +15179,18 @@
         <v>98</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>707</v>
+        <v>677</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" t="s" s="2">
-        <v>709</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -15124,7 +15238,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15133,7 +15247,7 @@
         <v>97</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>82</v>
+        <v>681</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>109</v>
@@ -15142,7 +15256,7 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
@@ -15151,7 +15265,7 @@
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>269</v>
+        <v>198</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
@@ -15160,7 +15274,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>711</v>
+        <v>82</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15168,10 +15282,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>712</v>
+        <v>683</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>713</v>
+        <v>683</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15194,18 +15308,18 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" t="s" s="2">
-        <v>716</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -15229,13 +15343,13 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>82</v>
+        <v>687</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>82</v>
+        <v>688</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -15253,7 +15367,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15280,7 +15394,7 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>718</v>
+        <v>198</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
@@ -15289,7 +15403,7 @@
         <v>82</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>719</v>
+        <v>82</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15297,10 +15411,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15323,20 +15437,18 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>722</v>
+        <v>227</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>723</v>
+        <v>691</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>724</v>
+        <v>692</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>726</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -15384,7 +15496,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>727</v>
+        <v>694</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15402,7 +15514,7 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>82</v>
+        <v>695</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
@@ -15411,7 +15523,7 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>728</v>
+        <v>696</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
@@ -15420,7 +15532,7 @@
         <v>82</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>729</v>
+        <v>82</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15428,10 +15540,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>730</v>
+        <v>697</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>731</v>
+        <v>697</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15457,17 +15569,15 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>732</v>
+        <v>698</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>733</v>
+        <v>699</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>735</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -15515,7 +15625,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>736</v>
+        <v>701</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15542,7 +15652,7 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>737</v>
+        <v>198</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
@@ -15551,18 +15661,18 @@
         <v>82</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>738</v>
+        <v>82</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>739</v>
+        <v>702</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>740</v>
+        <v>702</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15573,7 +15683,7 @@
         <v>83</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>98</v>
@@ -15582,23 +15692,21 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>140</v>
+        <v>703</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>741</v>
+        <v>704</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>742</v>
+        <v>705</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>744</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -15610,7 +15718,7 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>745</v>
+        <v>82</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>82</v>
@@ -15634,25 +15742,25 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>82</v>
+        <v>707</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>82</v>
+        <v>708</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>746</v>
+        <v>702</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
@@ -15664,68 +15772,70 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>82</v>
+        <v>709</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>82</v>
+        <v>710</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>747</v>
+        <v>711</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>82</v>
+        <v>712</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>748</v>
+        <v>82</v>
       </c>
       <c r="AS100" t="s" s="2">
-        <v>82</v>
+        <v>713</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>749</v>
+        <v>714</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C101" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>715</v>
+      </c>
       <c r="D101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>703</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>751</v>
+        <v>716</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>752</v>
+        <v>705</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>753</v>
+        <v>706</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15739,7 +15849,7 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>754</v>
+        <v>82</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>82</v>
@@ -15775,13 +15885,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>755</v>
+        <v>702</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -15793,36 +15903,36 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>709</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>82</v>
+        <v>710</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>756</v>
+        <v>711</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>82</v>
+        <v>712</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>757</v>
+        <v>82</v>
       </c>
       <c r="AS101" t="s" s="2">
-        <v>82</v>
+        <v>713</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>758</v>
+        <v>717</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>759</v>
+        <v>718</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15842,16 +15952,16 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>541</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>760</v>
+        <v>112</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>761</v>
+        <v>113</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15902,7 +16012,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>762</v>
+        <v>114</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15914,7 +16024,7 @@
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -15929,7 +16039,7 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>763</v>
+        <v>115</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
@@ -15938,7 +16048,7 @@
         <v>82</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>764</v>
+        <v>82</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>82</v>
@@ -15946,21 +16056,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>765</v>
+        <v>719</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>766</v>
+        <v>720</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -15969,19 +16079,19 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>333</v>
+        <v>118</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>767</v>
+        <v>119</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>768</v>
+        <v>120</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>769</v>
+        <v>121</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16019,31 +16129,31 @@
         <v>82</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>770</v>
+        <v>125</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -16058,7 +16168,7 @@
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>771</v>
+        <v>115</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>82</v>
@@ -16067,7 +16177,7 @@
         <v>82</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>772</v>
+        <v>82</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>82</v>
@@ -16075,10 +16185,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>773</v>
+        <v>721</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>774</v>
+        <v>722</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16104,13 +16214,13 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>617</v>
+        <v>677</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>618</v>
+        <v>678</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>619</v>
+        <v>679</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16160,7 +16270,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>620</v>
+        <v>680</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16169,7 +16279,7 @@
         <v>97</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>681</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>109</v>
@@ -16202,8 +16312,2852 @@
         <v>82</v>
       </c>
     </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS105" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS106" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS107" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR109" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AS109" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR110" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="AS110" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR113" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AS113" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS115" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR116" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AS116" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR117" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AS117" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR118" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AS118" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR119" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AS119" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR120" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS120" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ121" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR121" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AS121" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR122" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AS122" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ123" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR123" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="AS123" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ124" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR124" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AS124" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ125" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR125" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AS125" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR126" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS126" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AS104">
+  <autoFilter ref="A1:AS126">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16213,7 +19167,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI103">
+  <conditionalFormatting sqref="A2:AI125">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$104</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5201" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="777">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:23:45+00:00</t>
+    <t>2026-08-06T13:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1247,11 +1247,11 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel.coding.system pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07)</t>
+    <t>Slice sur securityLabel (pattern sur coding.system) pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07)</t>
   </si>
   <si>
     <t>niveauConfidentialite : [0..*] code</t>
@@ -1281,217 +1281,16 @@
     <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-Confidentiality"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
   </si>
   <si>
-    <t>DocumentReference.securityLabel:confidentiality.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.system</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-Confidentiality</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.version</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.code</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.display</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:confidentiality.text</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
     <t>DocumentReference.securityLabel:visibilityStatus</t>
   </si>
   <si>
@@ -1501,43 +1300,14 @@
     <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.version</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.code</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.display</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DocumentReference.securityLabel:visibilityStatus.text</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -2381,6 +2151,27 @@
     <t>DocumentReference.context.related.identifier.type.coding</t>
   </si>
   <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.id</t>
   </si>
   <si>
@@ -2399,15 +2190,54 @@
     <t>DocumentReference.context.related.identifier.type.coding.system</t>
   </si>
   <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
     <t>urn:ietf:rfc:3986</t>
   </si>
   <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.version</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.coding.version</t>
   </si>
   <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.code</t>
   </si>
   <si>
@@ -2417,22 +2247,98 @@
     <t>[CXi.5] Identifier Type Code : urn:ihe:iti:xds:2016:studyInstanceUID | urn:ihe:iti:xds:2013:order | urn:ihe:iti:xds:2013:accession</t>
   </si>
   <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.display</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.coding.display</t>
   </si>
   <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.coding.userSelected</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.coding.userSelected</t>
   </si>
   <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.type.text</t>
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>DocumentReference.context.related:referenceIdList.identifier.system</t>
@@ -2857,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS126"/>
+  <dimension ref="A1:AS104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.97265625" customWidth="true" bestFit="true"/>
@@ -2888,7 +2794,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="108.81640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="119.3046875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -7979,7 +7885,7 @@
         <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>82</v>
@@ -7998,7 +7904,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -8058,14 +7964,16 @@
         <v>395</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
       </c>
@@ -8074,28 +7982,32 @@
         <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>112</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -8104,7 +8016,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -8119,13 +8031,11 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -8143,87 +8053,85 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>114</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>115</v>
+        <v>397</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AS41" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>118</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>119</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -8260,22 +8168,22 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>125</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>84</v>
@@ -8284,7 +8192,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -8296,10 +8204,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>115</v>
+        <v>414</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8316,10 +8224,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8330,7 +8238,7 @@
         <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -8339,23 +8247,19 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>112</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -8403,19 +8307,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>414</v>
+        <v>114</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -8430,7 +8334,7 @@
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>415</v>
+        <v>115</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -8439,7 +8343,7 @@
         <v>82</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>82</v>
@@ -8447,21 +8351,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -8473,15 +8377,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -8530,19 +8436,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -8574,14 +8480,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>117</v>
+        <v>352</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -8594,24 +8500,26 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>118</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>119</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>120</v>
+        <v>354</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -8647,19 +8555,19 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>125</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8686,7 +8594,7 @@
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -8703,10 +8611,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8729,20 +8637,16 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>140</v>
+        <v>419</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -8751,7 +8655,7 @@
         <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>82</v>
@@ -8790,10 +8694,10 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>97</v>
@@ -8814,30 +8718,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8857,20 +8761,18 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8919,7 +8821,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8931,7 +8833,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8946,7 +8848,7 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>437</v>
+        <v>115</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -8955,7 +8857,7 @@
         <v>82</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AS47" t="s" s="2">
         <v>82</v>
@@ -8963,21 +8865,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8986,21 +8888,21 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>441</v>
+        <v>119</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -9036,31 +8938,31 @@
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -9075,7 +8977,7 @@
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>269</v>
+        <v>115</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -9084,7 +8986,7 @@
         <v>82</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AS48" t="s" s="2">
         <v>82</v>
@@ -9092,10 +8994,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9103,7 +9005,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>97</v>
@@ -9118,17 +9020,17 @@
         <v>98</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9141,7 +9043,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9153,13 +9055,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9177,7 +9079,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9195,7 +9097,7 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
@@ -9204,7 +9106,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -9213,18 +9115,18 @@
         <v>82</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9232,13 +9134,13 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -9247,19 +9149,17 @@
         <v>98</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>456</v>
+        <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9272,7 +9172,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9284,13 +9184,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -9308,7 +9208,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9323,10 +9223,10 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -9335,7 +9235,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9344,7 +9244,7 @@
         <v>82</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -9352,10 +9252,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9366,7 +9266,7 @@
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -9375,22 +9275,22 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>449</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9439,7 +9339,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9466,7 +9366,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -9475,34 +9375,32 @@
         <v>82</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -9511,19 +9409,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>259</v>
+        <v>458</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>389</v>
+        <v>460</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9536,7 +9434,7 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>82</v>
@@ -9548,11 +9446,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -9570,54 +9470,54 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>387</v>
+        <v>464</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>109</v>
+        <v>465</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>397</v>
+        <v>468</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>399</v>
+        <v>469</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>470</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9625,7 +9525,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>97</v>
@@ -9637,19 +9537,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>112</v>
+        <v>472</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -9697,7 +9601,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>114</v>
+        <v>476</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9709,13 +9613,13 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
@@ -9724,7 +9628,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>115</v>
+        <v>478</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9741,21 +9645,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -9764,21 +9668,23 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>118</v>
+        <v>449</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>119</v>
+        <v>480</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>120</v>
+        <v>481</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -9814,37 +9720,37 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>125</v>
+        <v>484</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
@@ -9853,7 +9759,7 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>115</v>
+        <v>486</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9870,10 +9776,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>409</v>
+        <v>487</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9881,10 +9787,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9896,19 +9802,17 @@
         <v>98</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>410</v>
+        <v>488</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>412</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>413</v>
+        <v>490</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9921,7 +9825,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -9957,13 +9861,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>414</v>
+        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9972,10 +9876,10 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
@@ -9984,7 +9888,7 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>415</v>
+        <v>495</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9993,18 +9897,18 @@
         <v>82</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10012,31 +9916,33 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>111</v>
+        <v>497</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>112</v>
+        <v>498</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>113</v>
+        <v>499</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -10084,7 +9990,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>114</v>
+        <v>501</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -10096,13 +10002,13 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -10111,7 +10017,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>115</v>
+        <v>478</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -10126,44 +10032,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>119</v>
+        <v>505</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>120</v>
+        <v>506</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>121</v>
+        <v>507</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10189,61 +10095,59 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>125</v>
+        <v>504</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>126</v>
+        <v>509</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>115</v>
+        <v>414</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>82</v>
@@ -10252,15 +10156,15 @@
         <v>82</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>514</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10274,7 +10178,7 @@
         <v>97</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -10283,20 +10187,18 @@
         <v>98</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>140</v>
+        <v>341</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>423</v>
+        <v>515</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>424</v>
+        <v>516</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -10305,7 +10207,7 @@
         <v>82</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>82</v>
@@ -10344,7 +10246,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10371,7 +10273,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>429</v>
+        <v>518</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10380,7 +10282,7 @@
         <v>82</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AS58" t="s" s="2">
         <v>82</v>
@@ -10388,10 +10290,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>519</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>519</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10411,20 +10313,18 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>433</v>
+        <v>112</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -10473,7 +10373,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>436</v>
+        <v>114</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10485,7 +10385,7 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -10500,7 +10400,7 @@
         <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>437</v>
+        <v>115</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -10509,7 +10409,7 @@
         <v>82</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AS59" t="s" s="2">
         <v>82</v>
@@ -10517,21 +10417,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -10540,21 +10440,21 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>119</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -10602,19 +10502,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>444</v>
+        <v>125</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -10629,7 +10529,7 @@
         <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>269</v>
+        <v>115</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -10638,7 +10538,7 @@
         <v>82</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AS60" t="s" s="2">
         <v>82</v>
@@ -10646,43 +10546,45 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>521</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>353</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -10731,19 +10633,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>451</v>
+        <v>356</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -10758,7 +10660,7 @@
         <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -10767,7 +10669,7 @@
         <v>82</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>453</v>
+        <v>82</v>
       </c>
       <c r="AS61" t="s" s="2">
         <v>82</v>
@@ -10775,10 +10677,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>487</v>
+        <v>522</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>522</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10789,7 +10691,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -10798,23 +10700,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>456</v>
+        <v>523</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>524</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -10862,13 +10760,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>461</v>
+        <v>522</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -10880,25 +10778,25 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>462</v>
+        <v>529</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AS62" t="s" s="2">
         <v>82</v>
@@ -10906,10 +10804,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10920,7 +10818,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10929,23 +10827,21 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>466</v>
+        <v>532</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>467</v>
+        <v>533</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10969,13 +10865,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10993,34 +10889,34 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>531</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>109</v>
+        <v>537</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>471</v>
+        <v>541</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -11029,18 +10925,18 @@
         <v>82</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11063,13 +10959,13 @@
         <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>341</v>
+        <v>543</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>490</v>
+        <v>544</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>491</v>
+        <v>545</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11120,13 +11016,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -11144,13 +11040,13 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>492</v>
+        <v>546</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>493</v>
+        <v>547</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>82</v>
@@ -11159,15 +11055,15 @@
         <v>82</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>550</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>550</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11291,10 +11187,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11364,16 +11260,16 @@
         <v>82</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>125</v>
@@ -11420,46 +11316,44 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>552</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>552</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>118</v>
+        <v>497</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>353</v>
+        <v>553</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>354</v>
+        <v>554</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -11507,25 +11401,25 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>356</v>
+        <v>556</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
@@ -11534,7 +11428,7 @@
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>198</v>
+        <v>560</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -11543,7 +11437,7 @@
         <v>82</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AS67" t="s" s="2">
         <v>82</v>
@@ -11551,10 +11445,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>562</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>562</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11562,7 +11456,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>97</v>
@@ -11577,20 +11471,24 @@
         <v>98</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q68" s="2"/>
+      <c r="Q68" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="R68" t="s" s="2">
         <v>82</v>
       </c>
@@ -11634,54 +11532,54 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>497</v>
+        <v>567</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>557</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>569</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>493</v>
+        <v>570</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>503</v>
+        <v>571</v>
       </c>
       <c r="AS68" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11689,13 +11587,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -11704,13 +11602,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>112</v>
+        <v>573</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>113</v>
+        <v>574</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11737,13 +11635,11 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11761,7 +11657,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>114</v>
+        <v>572</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11773,25 +11669,25 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>115</v>
+        <v>580</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>82</v>
+        <v>581</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
@@ -11800,29 +11696,29 @@
         <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>582</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>582</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -11831,18 +11727,20 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>119</v>
+        <v>583</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>120</v>
+        <v>584</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11866,61 +11764,59 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>125</v>
+        <v>582</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>126</v>
+        <v>576</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>115</v>
+        <v>580</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11929,15 +11825,15 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>82</v>
+        <v>589</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>590</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>590</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11951,27 +11847,25 @@
         <v>97</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>175</v>
+        <v>591</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>508</v>
+        <v>592</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>509</v>
+        <v>593</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>510</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11983,7 +11877,7 @@
         <v>82</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>82</v>
@@ -11995,13 +11889,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -12019,7 +11913,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>590</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -12037,36 +11931,36 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>516</v>
+        <v>295</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>518</v>
+        <v>595</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>518</v>
+        <v>595</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12074,33 +11968,31 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>520</v>
+        <v>113</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>521</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -12112,7 +12004,7 @@
         <v>82</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>82</v>
@@ -12124,13 +12016,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -12148,7 +12040,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>523</v>
+        <v>114</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12160,13 +12052,13 @@
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>82</v>
@@ -12175,7 +12067,7 @@
         <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>526</v>
+        <v>115</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>82</v>
@@ -12192,21 +12084,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>596</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>596</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -12218,20 +12110,18 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>528</v>
+        <v>118</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>529</v>
+        <v>119</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>530</v>
+        <v>120</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -12267,31 +12157,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>533</v>
+        <v>125</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -12306,7 +12196,7 @@
         <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>534</v>
+        <v>115</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>82</v>
@@ -12315,7 +12205,7 @@
         <v>82</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>82</v>
@@ -12323,10 +12213,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>536</v>
+        <v>597</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>536</v>
+        <v>597</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12334,7 +12224,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>97</v>
@@ -12349,20 +12239,18 @@
         <v>98</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>537</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>538</v>
+        <v>598</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -12374,7 +12262,7 @@
         <v>82</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>82</v>
@@ -12410,7 +12298,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>543</v>
+        <v>601</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12419,16 +12307,16 @@
         <v>97</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>544</v>
+        <v>109</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>546</v>
+        <v>603</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12437,7 +12325,7 @@
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>547</v>
+        <v>198</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>82</v>
@@ -12446,7 +12334,7 @@
         <v>82</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="AS74" t="s" s="2">
         <v>82</v>
@@ -12454,10 +12342,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>549</v>
+        <v>604</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>549</v>
+        <v>604</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12465,7 +12353,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>97</v>
@@ -12480,20 +12368,18 @@
         <v>98</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>550</v>
+        <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>551</v>
+        <v>605</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>552</v>
+        <v>606</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -12517,13 +12403,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -12541,7 +12427,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>555</v>
+        <v>610</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12559,7 +12445,7 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
@@ -12568,7 +12454,7 @@
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>557</v>
+        <v>198</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>82</v>
@@ -12585,10 +12471,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12596,7 +12482,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>97</v>
@@ -12611,20 +12497,18 @@
         <v>98</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>528</v>
+        <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>559</v>
+        <v>612</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>560</v>
+        <v>613</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -12672,7 +12556,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>563</v>
+        <v>615</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12690,7 +12574,7 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>564</v>
+        <v>616</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
@@ -12699,7 +12583,7 @@
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>565</v>
+        <v>617</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -12716,10 +12600,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>566</v>
+        <v>618</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>566</v>
+        <v>618</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12727,7 +12611,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>97</v>
@@ -12745,15 +12629,15 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -12765,7 +12649,7 @@
         <v>82</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>82</v>
@@ -12801,7 +12685,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>571</v>
+        <v>622</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12816,10 +12700,10 @@
         <v>109</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>572</v>
+        <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
@@ -12828,7 +12712,7 @@
         <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>574</v>
+        <v>198</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>82</v>
@@ -12843,12 +12727,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>575</v>
+        <v>623</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12856,10 +12740,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>98</v>
@@ -12868,21 +12752,21 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>576</v>
+        <v>624</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -12918,25 +12802,25 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -12945,22 +12829,22 @@
         <v>109</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>581</v>
+        <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>582</v>
+        <v>630</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>557</v>
+        <v>632</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>82</v>
@@ -12969,47 +12853,49 @@
         <v>82</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>153</v>
+        <v>624</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>584</v>
+        <v>637</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>585</v>
+        <v>626</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>586</v>
+        <v>627</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -13035,11 +12921,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>587</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -13057,37 +12945,37 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>583</v>
+        <v>623</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>588</v>
+        <v>109</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>590</v>
+        <v>630</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>591</v>
+        <v>631</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>493</v>
+        <v>632</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>592</v>
+        <v>633</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>82</v>
@@ -13096,15 +12984,15 @@
         <v>82</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>590</v>
+        <v>634</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>593</v>
+        <v>639</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13112,32 +13000,30 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>341</v>
+        <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>594</v>
+        <v>112</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13186,7 +13072,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>593</v>
+        <v>114</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13198,7 +13084,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -13213,7 +13099,7 @@
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>597</v>
+        <v>115</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>82</v>
@@ -13230,21 +13116,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>598</v>
+        <v>641</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -13256,15 +13142,17 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -13301,31 +13189,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -13357,21 +13245,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>599</v>
+        <v>642</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>599</v>
+        <v>643</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -13380,19 +13268,19 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>119</v>
+        <v>598</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>120</v>
+        <v>599</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>121</v>
+        <v>600</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13442,19 +13330,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>125</v>
+        <v>601</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -13469,7 +13357,7 @@
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -13486,46 +13374,44 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>600</v>
+        <v>644</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>98</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>353</v>
+        <v>605</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>354</v>
+        <v>606</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -13549,13 +13435,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -13573,19 +13459,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>356</v>
+        <v>610</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -13615,12 +13501,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>601</v>
+        <v>646</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>601</v>
+        <v>647</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13631,27 +13517,29 @@
         <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>602</v>
+        <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>613</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -13700,13 +13588,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -13718,22 +13606,22 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>82</v>
@@ -13744,10 +13632,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>610</v>
+        <v>648</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>610</v>
+        <v>649</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13758,7 +13646,7 @@
         <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -13770,17 +13658,15 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>611</v>
+        <v>112</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -13805,13 +13691,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -13829,34 +13715,34 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>610</v>
+        <v>114</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>620</v>
+        <v>115</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>82</v>
@@ -13868,46 +13754,48 @@
         <v>82</v>
       </c>
       <c r="AS85" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>621</v>
+        <v>651</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>622</v>
+        <v>118</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>623</v>
+        <v>119</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -13944,31 +13832,31 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>621</v>
+        <v>125</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -13980,13 +13868,13 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>626</v>
+        <v>115</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>627</v>
+        <v>82</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>82</v>
@@ -13995,15 +13883,15 @@
         <v>82</v>
       </c>
       <c r="AS86" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -14020,22 +13908,26 @@
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>112</v>
+        <v>654</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -14059,13 +13951,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>659</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -14083,7 +13975,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>114</v>
+        <v>660</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14095,7 +13987,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -14110,7 +14002,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>115</v>
+        <v>661</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -14119,7 +14011,7 @@
         <v>82</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AS87" t="s" s="2">
         <v>82</v>
@@ -14127,21 +14019,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>630</v>
+        <v>662</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>630</v>
+        <v>663</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -14150,21 +14042,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>119</v>
+        <v>664</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>120</v>
+        <v>665</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -14188,43 +14082,43 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>82</v>
+        <v>668</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>125</v>
+        <v>670</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -14239,7 +14133,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>115</v>
+        <v>661</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14248,7 +14142,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>82</v>
+        <v>671</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14256,10 +14150,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>631</v>
+        <v>672</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>631</v>
+        <v>673</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14267,7 +14161,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>97</v>
@@ -14279,20 +14173,18 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>576</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>632</v>
+        <v>112</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>634</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -14341,7 +14233,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>635</v>
+        <v>114</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14350,16 +14242,16 @@
         <v>97</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>82</v>
@@ -14368,7 +14260,7 @@
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>639</v>
+        <v>115</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>82</v>
@@ -14377,7 +14269,7 @@
         <v>82</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>640</v>
+        <v>82</v>
       </c>
       <c r="AS89" t="s" s="2">
         <v>82</v>
@@ -14385,21 +14277,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>641</v>
+        <v>674</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>641</v>
+        <v>675</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -14408,27 +14300,25 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>576</v>
+        <v>118</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>642</v>
+        <v>119</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>643</v>
+        <v>120</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>644</v>
+        <v>121</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>645</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
         <v>82</v>
       </c>
@@ -14460,37 +14350,37 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>646</v>
+        <v>125</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>82</v>
@@ -14499,7 +14389,7 @@
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>649</v>
+        <v>115</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>82</v>
@@ -14508,18 +14398,18 @@
         <v>82</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="AS90" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14527,31 +14417,35 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J91" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K91" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>652</v>
+        <v>678</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>679</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>681</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -14575,11 +14469,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -14597,54 +14493,54 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>655</v>
+        <v>109</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>659</v>
+        <v>683</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>82</v>
+        <v>684</v>
       </c>
       <c r="AS91" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14652,13 +14548,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
@@ -14667,20 +14563,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>662</v>
+        <v>112</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -14704,11 +14596,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>666</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -14726,7 +14620,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>661</v>
+        <v>114</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14738,25 +14632,25 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>668</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>659</v>
+        <v>115</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>82</v>
@@ -14765,29 +14659,29 @@
         <v>82</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>668</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>669</v>
+        <v>688</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>82</v>
@@ -14796,15 +14690,17 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>670</v>
+        <v>118</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>671</v>
+        <v>119</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -14841,31 +14737,31 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>669</v>
+        <v>125</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -14877,13 +14773,13 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>295</v>
+        <v>115</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>82</v>
@@ -14892,15 +14788,15 @@
         <v>82</v>
       </c>
       <c r="AS93" t="s" s="2">
-        <v>673</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14920,19 +14816,23 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>112</v>
+        <v>691</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -14941,7 +14841,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>82</v>
+        <v>695</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14980,7 +14880,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>114</v>
+        <v>696</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14992,7 +14892,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -15007,7 +14907,7 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>115</v>
+        <v>697</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
@@ -15016,7 +14916,7 @@
         <v>82</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>82</v>
+        <v>698</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -15024,21 +14924,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>675</v>
+        <v>699</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -15047,19 +14947,19 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>119</v>
+        <v>701</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>120</v>
+        <v>702</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>121</v>
+        <v>703</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15097,31 +14997,31 @@
         <v>82</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>125</v>
+        <v>704</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -15136,7 +15036,7 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>115</v>
+        <v>705</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>82</v>
@@ -15145,18 +15045,18 @@
         <v>82</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>82</v>
+        <v>706</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>676</v>
+        <v>708</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15170,7 +15070,7 @@
         <v>97</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -15179,18 +15079,18 @@
         <v>98</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>677</v>
+        <v>709</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>711</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -15238,7 +15138,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>680</v>
+        <v>712</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15247,7 +15147,7 @@
         <v>97</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>681</v>
+        <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>109</v>
@@ -15256,7 +15156,7 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>682</v>
+        <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
@@ -15265,7 +15165,7 @@
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>198</v>
+        <v>269</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
@@ -15274,7 +15174,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>82</v>
+        <v>713</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15282,10 +15182,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15308,18 +15208,18 @@
         <v>98</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>684</v>
+        <v>716</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>718</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -15343,13 +15243,13 @@
         <v>82</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>688</v>
+        <v>82</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -15367,7 +15267,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>689</v>
+        <v>719</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15394,7 +15294,7 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>198</v>
+        <v>720</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
@@ -15403,7 +15303,7 @@
         <v>82</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>82</v>
+        <v>721</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15411,10 +15311,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>690</v>
+        <v>722</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>690</v>
+        <v>723</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15437,18 +15337,20 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>227</v>
+        <v>724</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>691</v>
+        <v>725</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>692</v>
+        <v>726</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>727</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>728</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -15496,7 +15398,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>694</v>
+        <v>729</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15514,7 +15416,7 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
@@ -15523,7 +15425,7 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>696</v>
+        <v>730</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
@@ -15532,7 +15434,7 @@
         <v>82</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>82</v>
+        <v>731</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15540,10 +15442,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>697</v>
+        <v>732</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>697</v>
+        <v>733</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15569,15 +15471,17 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>699</v>
+        <v>735</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>736</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>737</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -15625,7 +15529,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15652,7 +15556,7 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>198</v>
+        <v>739</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
@@ -15661,18 +15565,18 @@
         <v>82</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>82</v>
+        <v>740</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>702</v>
+        <v>741</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>702</v>
+        <v>742</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15683,7 +15587,7 @@
         <v>83</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>98</v>
@@ -15692,21 +15596,23 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>703</v>
+        <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>705</v>
+        <v>744</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>745</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>746</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -15718,7 +15624,7 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>82</v>
+        <v>747</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>82</v>
@@ -15742,25 +15648,25 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>707</v>
+        <v>82</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>708</v>
+        <v>82</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>702</v>
+        <v>748</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
@@ -15772,70 +15678,68 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>709</v>
+        <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>710</v>
+        <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>711</v>
+        <v>749</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>712</v>
+        <v>82</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>82</v>
+        <v>750</v>
       </c>
       <c r="AS100" t="s" s="2">
-        <v>713</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>714</v>
+        <v>751</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>715</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>703</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>716</v>
+        <v>753</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>705</v>
+        <v>754</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>706</v>
+        <v>755</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15849,7 +15753,7 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>82</v>
+        <v>756</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>82</v>
@@ -15885,13 +15789,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>702</v>
+        <v>757</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -15903,36 +15807,36 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>709</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>710</v>
+        <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>711</v>
+        <v>758</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>712</v>
+        <v>82</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>82</v>
+        <v>759</v>
       </c>
       <c r="AS101" t="s" s="2">
-        <v>713</v>
+        <v>82</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>717</v>
+        <v>760</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>718</v>
+        <v>761</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15952,16 +15856,16 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>543</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>112</v>
+        <v>762</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>113</v>
+        <v>763</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -16012,7 +15916,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>114</v>
+        <v>764</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -16024,7 +15928,7 @@
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -16039,7 +15943,7 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>115</v>
+        <v>765</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
@@ -16048,7 +15952,7 @@
         <v>82</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>82</v>
+        <v>766</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>82</v>
@@ -16056,21 +15960,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -16079,19 +15983,19 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>118</v>
+        <v>333</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>119</v>
+        <v>769</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>120</v>
+        <v>770</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>121</v>
+        <v>771</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16129,31 +16033,31 @@
         <v>82</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>125</v>
+        <v>772</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>82</v>
@@ -16168,7 +16072,7 @@
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>115</v>
+        <v>773</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>82</v>
@@ -16177,7 +16081,7 @@
         <v>82</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>82</v>
+        <v>774</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>82</v>
@@ -16185,10 +16089,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>721</v>
+        <v>775</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>722</v>
+        <v>776</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16214,13 +16118,13 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>677</v>
+        <v>619</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>678</v>
+        <v>620</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>679</v>
+        <v>621</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16270,7 +16174,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>680</v>
+        <v>622</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>
@@ -16279,7 +16183,7 @@
         <v>97</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>681</v>
+        <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>109</v>
@@ -16312,2852 +16216,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS105" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS106" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS107" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR109" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AS109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR110" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="AS110" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS112" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR113" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AS113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR116" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AS116" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR117" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AS117" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR118" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AS118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR119" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AS119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR120" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AS120" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="P121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR121" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AS121" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="P122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR122" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="AS122" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR123" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="AS123" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR124" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="AS124" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR125" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="AS125" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS126" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AS126">
+  <autoFilter ref="A1:AS104">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19167,7 +16227,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI125">
+  <conditionalFormatting sqref="A2:AI103">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:28:00+00:00</t>
+    <t>2026-08-06T13:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1247,7 +1247,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:33:58+00:00</t>
+    <t>2026-08-06T13:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1251,7 +1251,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel (pattern sur coding.system) pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : confidentiality est discriminée par son required binding (ValueSet fermé v3-ConfidentialityClassification), visibilityStatus par un pattern sur coding.system (JDV_J110-StatutVisibiliteDocument-CISIS)</t>
   </si>
   <si>
     <t>niveauConfidentialite : [0..*] code</t>
@@ -1279,13 +1279,6 @@
   </si>
   <si>
     <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/v3-Confidentiality"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
@@ -2794,7 +2787,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="119.3046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="253.52734375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -7885,7 +7878,7 @@
         <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>82</v>
@@ -7904,7 +7897,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7966,13 +7959,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
@@ -7997,7 +7990,7 @@
         <v>259</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>389</v>
@@ -8016,7 +8009,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -8035,7 +8028,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -8097,10 +8090,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8126,10 +8119,10 @@
         <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8180,7 +8173,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>97</v>
@@ -8204,10 +8197,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8224,10 +8217,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8351,10 +8344,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8480,10 +8473,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8611,10 +8604,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8637,13 +8630,13 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8694,7 +8687,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>97</v>
@@ -8718,30 +8711,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AQ46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR46" t="s" s="2">
+      <c r="AS46" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8865,10 +8858,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8994,10 +8987,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9023,14 +9016,14 @@
         <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9043,7 +9036,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9058,28 +9051,28 @@
         <v>242</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="Z49" t="s" s="2">
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9097,25 +9090,25 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -9123,10 +9116,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9152,14 +9145,14 @@
         <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9172,7 +9165,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9208,7 +9201,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9223,19 +9216,19 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9252,10 +9245,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9278,19 +9271,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9339,7 +9332,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9366,16 +9359,16 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -9383,10 +9376,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9409,19 +9402,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9434,79 +9427,79 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AG52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
+      <c r="AK52" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -9514,10 +9507,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9540,19 +9533,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9601,7 +9594,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9619,16 +9612,16 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9645,10 +9638,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9671,19 +9664,19 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9732,7 +9725,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9750,16 +9743,16 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9776,10 +9769,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9805,14 +9798,14 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9825,43 +9818,43 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9876,19 +9869,19 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9905,10 +9898,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9931,17 +9924,17 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9990,7 +9983,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -10005,11 +9998,11 @@
         <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
       </c>
@@ -10017,7 +10010,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -10034,10 +10027,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10063,13 +10056,13 @@
         <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10099,56 +10092,56 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="AK57" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AK57" t="s" s="2">
+      <c r="AL57" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AQ57" t="s" s="2">
         <v>82</v>
       </c>
@@ -10156,15 +10149,15 @@
         <v>82</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10190,13 +10183,13 @@
         <v>341</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10246,7 +10239,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10273,7 +10266,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10290,10 +10283,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10417,10 +10410,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10546,10 +10539,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10677,10 +10670,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10703,13 +10696,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10760,7 +10753,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10778,22 +10771,22 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10804,10 +10797,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10833,13 +10826,13 @@
         <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10868,11 +10861,11 @@
         <v>165</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10889,7 +10882,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10901,23 +10894,23 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AK63" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AK63" t="s" s="2">
+      <c r="AL63" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AO63" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10928,15 +10921,15 @@
         <v>82</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10959,13 +10952,13 @@
         <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11016,7 +11009,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -11040,30 +11033,30 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="AP64" t="s" s="2">
+      <c r="AQ64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS64" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS64" t="s" s="2">
-        <v>549</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11187,10 +11180,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11316,10 +11309,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11342,16 +11335,16 @@
         <v>98</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11401,43 +11394,43 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AS67" t="s" s="2">
         <v>82</v>
@@ -11445,10 +11438,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11471,69 +11464,69 @@
         <v>98</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="R68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
@@ -11541,34 +11534,34 @@
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -11576,10 +11569,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11605,10 +11598,10 @@
         <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11639,56 +11632,56 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
+      <c r="AK69" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AK69" t="s" s="2">
+      <c r="AL69" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AO69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AP69" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11696,15 +11689,15 @@
         <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11730,16 +11723,16 @@
         <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11768,55 +11761,55 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AA70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AK70" t="s" s="2">
+      <c r="AL70" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AP70" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11825,15 +11818,15 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11856,13 +11849,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11913,7 +11906,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11952,15 +11945,15 @@
         <v>82</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12084,10 +12077,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12213,10 +12206,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12242,13 +12235,13 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12298,16 +12291,16 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI74" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>109</v>
@@ -12316,7 +12309,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12342,10 +12335,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12371,13 +12364,13 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12406,28 +12399,28 @@
         <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12471,10 +12464,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12500,13 +12493,13 @@
         <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12556,7 +12549,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12574,16 +12567,16 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -12600,10 +12593,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12629,13 +12622,13 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12685,7 +12678,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12729,10 +12722,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12755,16 +12748,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12802,10 +12795,10 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AC78" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
@@ -12814,7 +12807,7 @@
         <v>124</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12832,39 +12825,39 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AP78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS78" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS78" t="s" s="2">
-        <v>634</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>82</v>
@@ -12886,16 +12879,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12945,7 +12938,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12963,36 +12956,36 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="AP79" t="s" s="2">
+      <c r="AQ79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS79" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS79" t="s" s="2">
-        <v>634</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13116,10 +13109,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13245,10 +13238,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13274,13 +13267,13 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13330,16 +13323,16 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>109</v>
@@ -13374,10 +13367,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13403,13 +13396,13 @@
         <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13438,28 +13431,28 @@
         <v>157</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13503,10 +13496,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13532,13 +13525,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13588,7 +13581,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13615,7 +13608,7 @@
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -13632,10 +13625,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13759,10 +13752,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13888,10 +13881,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13917,16 +13910,16 @@
         <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13954,28 +13947,28 @@
         <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="Z87" t="s" s="2">
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -14002,7 +13995,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -14019,10 +14012,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14048,16 +14041,16 @@
         <v>259</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -14085,28 +14078,28 @@
         <v>157</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14133,7 +14126,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14142,7 +14135,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14150,10 +14143,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14277,10 +14270,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14406,10 +14399,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14435,16 +14428,16 @@
         <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14493,7 +14486,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14520,16 +14513,16 @@
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="AS91" t="s" s="2">
         <v>82</v>
@@ -14537,10 +14530,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14664,10 +14657,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14793,10 +14786,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14822,16 +14815,16 @@
         <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14841,46 +14834,46 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14907,16 +14900,16 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR94" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14924,10 +14917,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14953,13 +14946,13 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15009,7 +15002,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15036,16 +15029,16 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
@@ -15053,10 +15046,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>708</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15082,14 +15075,14 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15138,7 +15131,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15174,7 +15167,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15182,10 +15175,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15211,14 +15204,14 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15267,7 +15260,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15294,16 +15287,16 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR97" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15311,10 +15304,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15337,19 +15330,19 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -15398,7 +15391,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15425,16 +15418,16 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR98" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15442,10 +15435,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15471,16 +15464,16 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -15529,7 +15522,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15556,16 +15549,16 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
@@ -15573,10 +15566,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15602,16 +15595,16 @@
         <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15624,43 +15617,43 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15687,16 +15680,16 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR100" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR100" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
@@ -15704,10 +15697,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15733,13 +15726,13 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15753,43 +15746,43 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15816,16 +15809,16 @@
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR101" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15833,10 +15826,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15859,13 +15852,13 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15916,7 +15909,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15943,16 +15936,16 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR102" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>82</v>
@@ -15960,10 +15953,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15989,13 +15982,13 @@
         <v>333</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16045,7 +16038,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16072,16 +16065,16 @@
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR103" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR103" t="s" s="2">
-        <v>774</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>82</v>
@@ -16089,10 +16082,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16118,13 +16111,13 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16174,7 +16167,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="775">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:37:30+00:00</t>
+    <t>2026-08-06T13:40:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1251,7 +1251,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : confidentiality est discriminée par son required binding (ValueSet fermé v3-ConfidentialityClassification), visibilityStatus par un pattern sur coding.system (JDV_J110-StatutVisibiliteDocument-CISIS)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>niveauConfidentialite : [0..*] code</t>
@@ -1291,13 +1291,6 @@
   </si>
   <si>
     <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_A07-StatutVisibiliteDocument/FHIR/TRE-A07-StatutVisibiliteDocument"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
@@ -2787,7 +2780,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="253.52734375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="249.46875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -8009,7 +8002,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -8028,7 +8021,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -8090,10 +8083,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8119,10 +8112,10 @@
         <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8173,7 +8166,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>97</v>
@@ -8197,10 +8190,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8217,10 +8210,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8344,10 +8337,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8473,10 +8466,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8604,10 +8597,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8630,13 +8623,13 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8687,7 +8680,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>97</v>
@@ -8711,30 +8704,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AQ46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR46" t="s" s="2">
+      <c r="AS46" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8858,10 +8851,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8987,10 +8980,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9016,14 +9009,14 @@
         <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9036,7 +9029,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9051,28 +9044,28 @@
         <v>242</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Z49" t="s" s="2">
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9090,25 +9083,25 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -9116,10 +9109,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9145,14 +9138,14 @@
         <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9165,7 +9158,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9201,7 +9194,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9216,19 +9209,19 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9245,10 +9238,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9271,19 +9264,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9332,7 +9325,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9359,16 +9352,16 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -9376,10 +9369,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9402,19 +9395,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9427,79 +9420,79 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AG52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
+      <c r="AK52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -9507,10 +9500,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9533,19 +9526,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9594,7 +9587,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9612,16 +9605,16 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9638,10 +9631,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9664,19 +9657,19 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9725,7 +9718,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9743,16 +9736,16 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9769,10 +9762,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9798,14 +9791,14 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9818,43 +9811,43 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9869,19 +9862,19 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9898,10 +9891,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9924,17 +9917,17 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9983,7 +9976,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9998,11 +9991,11 @@
         <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
       </c>
@@ -10010,7 +10003,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -10027,10 +10020,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10056,13 +10049,13 @@
         <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10092,56 +10085,56 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="AK57" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK57" t="s" s="2">
+      <c r="AL57" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AQ57" t="s" s="2">
         <v>82</v>
       </c>
@@ -10149,15 +10142,15 @@
         <v>82</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10183,13 +10176,13 @@
         <v>341</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10239,7 +10232,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10266,7 +10259,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10283,10 +10276,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10410,10 +10403,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10539,10 +10532,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10670,10 +10663,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10696,13 +10689,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10753,7 +10746,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10771,22 +10764,22 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10797,10 +10790,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10826,13 +10819,13 @@
         <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10861,11 +10854,11 @@
         <v>165</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10882,7 +10875,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10894,23 +10887,23 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AK63" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AK63" t="s" s="2">
+      <c r="AL63" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AO63" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10921,15 +10914,15 @@
         <v>82</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10952,13 +10945,13 @@
         <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11009,7 +11002,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -11033,30 +11026,30 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AP64" t="s" s="2">
+      <c r="AQ64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS64" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS64" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11180,10 +11173,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11309,10 +11302,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11335,16 +11328,16 @@
         <v>98</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11394,43 +11387,43 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AS67" t="s" s="2">
         <v>82</v>
@@ -11438,10 +11431,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11464,69 +11457,69 @@
         <v>98</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="R68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
@@ -11534,34 +11527,34 @@
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -11569,10 +11562,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11598,10 +11591,10 @@
         <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11632,56 +11625,56 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
+      <c r="AK69" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AK69" t="s" s="2">
+      <c r="AL69" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AO69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AP69" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11689,15 +11682,15 @@
         <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11723,16 +11716,16 @@
         <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11761,55 +11754,55 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AA70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AK70" t="s" s="2">
+      <c r="AL70" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>588</v>
-      </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="AP70" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11818,15 +11811,15 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11849,13 +11842,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11906,7 +11899,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11945,15 +11938,15 @@
         <v>82</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12077,10 +12070,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12206,10 +12199,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12235,13 +12228,13 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12291,16 +12284,16 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI74" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>109</v>
@@ -12309,7 +12302,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12335,10 +12328,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12364,13 +12357,13 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12399,28 +12392,28 @@
         <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12464,10 +12457,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12493,13 +12486,13 @@
         <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12549,7 +12542,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12567,16 +12560,16 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -12593,10 +12586,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12622,13 +12615,13 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12678,7 +12671,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12722,10 +12715,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12748,16 +12741,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12795,10 +12788,10 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AC78" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
@@ -12807,7 +12800,7 @@
         <v>124</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12825,39 +12818,39 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AP78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS78" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS78" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>82</v>
@@ -12879,16 +12872,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12938,7 +12931,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12956,36 +12949,36 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AP79" t="s" s="2">
+      <c r="AQ79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS79" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS79" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13109,10 +13102,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13238,10 +13231,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13267,13 +13260,13 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13323,16 +13316,16 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>109</v>
@@ -13367,10 +13360,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13396,13 +13389,13 @@
         <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13431,28 +13424,28 @@
         <v>157</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13496,10 +13489,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13525,13 +13518,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13581,7 +13574,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13608,7 +13601,7 @@
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -13625,10 +13618,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13752,10 +13745,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13881,10 +13874,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13910,16 +13903,16 @@
         <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13947,28 +13940,28 @@
         <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="Z87" t="s" s="2">
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13995,7 +13988,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -14012,10 +14005,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14041,16 +14034,16 @@
         <v>259</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -14078,28 +14071,28 @@
         <v>157</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14126,7 +14119,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14135,7 +14128,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14143,10 +14136,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14270,10 +14263,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14399,10 +14392,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14428,16 +14421,16 @@
         <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14486,7 +14479,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14513,16 +14506,16 @@
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AS91" t="s" s="2">
         <v>82</v>
@@ -14530,10 +14523,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14657,10 +14650,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14786,10 +14779,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14815,16 +14808,16 @@
         <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14834,46 +14827,46 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14900,16 +14893,16 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR94" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14917,10 +14910,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14946,13 +14939,13 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -15002,7 +14995,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15029,16 +15022,16 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
@@ -15046,10 +15039,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15075,14 +15068,14 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15131,7 +15124,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15167,7 +15160,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15175,10 +15168,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15204,14 +15197,14 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15260,7 +15253,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15287,16 +15280,16 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR97" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15304,10 +15297,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15330,19 +15323,19 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -15391,7 +15384,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15418,16 +15411,16 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR98" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15435,10 +15428,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15464,16 +15457,16 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -15522,7 +15515,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15549,16 +15542,16 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
@@ -15566,10 +15559,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15595,16 +15588,16 @@
         <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15617,43 +15610,43 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15680,16 +15673,16 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR100" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR100" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
@@ -15697,10 +15690,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15726,13 +15719,13 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15746,43 +15739,43 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15809,16 +15802,16 @@
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR101" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15826,10 +15819,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15852,13 +15845,13 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15909,7 +15902,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15936,16 +15929,16 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR102" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>82</v>
@@ -15953,10 +15946,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15982,13 +15975,13 @@
         <v>333</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16038,7 +16031,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16065,16 +16058,16 @@
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR103" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR103" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>82</v>
@@ -16082,10 +16075,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16111,13 +16104,13 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16167,7 +16160,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:40:23+00:00</t>
+    <t>2026-08-06T13:54:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1279,6 +1279,9 @@
   </si>
   <si>
     <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
+  </si>
+  <si>
+    <t>En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
@@ -7855,7 +7858,7 @@
         <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>390</v>
@@ -7890,7 +7893,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7952,13 +7955,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
@@ -7983,7 +7986,7 @@
         <v>259</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>389</v>
@@ -8021,7 +8024,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -8083,10 +8086,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8112,10 +8115,10 @@
         <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8166,7 +8169,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>97</v>
@@ -8190,10 +8193,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8210,10 +8213,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8337,10 +8340,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8466,10 +8469,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8597,10 +8600,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8623,13 +8626,13 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8680,7 +8683,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>97</v>
@@ -8704,30 +8707,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8851,10 +8854,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8980,10 +8983,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9009,14 +9012,14 @@
         <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9029,7 +9032,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9044,10 +9047,10 @@
         <v>242</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9065,7 +9068,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9083,7 +9086,7 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
@@ -9092,7 +9095,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -9101,7 +9104,7 @@
         <v>82</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -9109,10 +9112,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9138,14 +9141,14 @@
         <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9158,7 +9161,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9194,7 +9197,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9209,10 +9212,10 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -9221,7 +9224,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9238,10 +9241,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9264,19 +9267,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9325,7 +9328,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9352,7 +9355,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -9361,7 +9364,7 @@
         <v>82</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -9369,10 +9372,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9395,19 +9398,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9420,7 +9423,7 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>82</v>
@@ -9456,7 +9459,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9468,13 +9471,13 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
@@ -9483,7 +9486,7 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -9492,7 +9495,7 @@
         <v>82</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -9500,10 +9503,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9526,19 +9529,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9587,7 +9590,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9605,7 +9608,7 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
@@ -9614,7 +9617,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9631,10 +9634,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9657,19 +9660,19 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9718,7 +9721,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9736,7 +9739,7 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
@@ -9745,7 +9748,7 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9762,10 +9765,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9791,14 +9794,14 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9811,7 +9814,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -9847,7 +9850,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9862,10 +9865,10 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
@@ -9874,7 +9877,7 @@
         <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9891,10 +9894,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9917,17 +9920,17 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9976,7 +9979,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9991,10 +9994,10 @@
         <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -10003,7 +10006,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -10020,10 +10023,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10049,13 +10052,13 @@
         <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10085,7 +10088,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -10103,7 +10106,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -10115,42 +10118,42 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS57" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS57" t="s" s="2">
-        <v>509</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10176,13 +10179,13 @@
         <v>341</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10232,7 +10235,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10259,7 +10262,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10276,10 +10279,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10403,10 +10406,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10532,10 +10535,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10663,10 +10666,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10689,13 +10692,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10746,7 +10749,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10764,22 +10767,22 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10790,10 +10793,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10819,13 +10822,13 @@
         <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10854,10 +10857,10 @@
         <v>165</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10875,7 +10878,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10887,42 +10890,42 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS63" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS63" t="s" s="2">
-        <v>537</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10945,13 +10948,13 @@
         <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11002,7 +11005,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -11026,13 +11029,13 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>82</v>
@@ -11041,15 +11044,15 @@
         <v>82</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11173,10 +11176,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11302,10 +11305,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11328,16 +11331,16 @@
         <v>98</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11387,7 +11390,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11396,16 +11399,16 @@
         <v>97</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
@@ -11414,7 +11417,7 @@
         <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -11423,7 +11426,7 @@
         <v>82</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AS67" t="s" s="2">
         <v>82</v>
@@ -11431,10 +11434,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11457,23 +11460,23 @@
         <v>98</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="R68" t="s" s="2">
         <v>82</v>
@@ -11518,7 +11521,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11527,16 +11530,16 @@
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
@@ -11545,7 +11548,7 @@
         <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
@@ -11554,7 +11557,7 @@
         <v>82</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -11562,10 +11565,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11591,10 +11594,10 @@
         <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11625,7 +11628,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11643,7 +11646,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11655,42 +11658,42 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS69" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS69" t="s" s="2">
-        <v>576</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11716,16 +11719,16 @@
         <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11754,7 +11757,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -11772,7 +11775,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11784,26 +11787,26 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AP70" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11811,15 +11814,15 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11842,13 +11845,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11899,7 +11902,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11938,15 +11941,15 @@
         <v>82</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12070,10 +12073,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12199,10 +12202,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12228,13 +12231,13 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12284,7 +12287,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12293,7 +12296,7 @@
         <v>97</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>109</v>
@@ -12302,7 +12305,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12328,10 +12331,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12357,13 +12360,13 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12392,10 +12395,10 @@
         <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -12413,7 +12416,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12457,10 +12460,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12486,13 +12489,13 @@
         <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12542,7 +12545,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12560,7 +12563,7 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
@@ -12569,7 +12572,7 @@
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -12586,10 +12589,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12615,13 +12618,13 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12671,7 +12674,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12715,10 +12718,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12741,16 +12744,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12788,10 +12791,10 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
@@ -12800,7 +12803,7 @@
         <v>124</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12818,19 +12821,19 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>82</v>
@@ -12839,18 +12842,18 @@
         <v>82</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>82</v>
@@ -12872,16 +12875,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12931,7 +12934,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12949,19 +12952,19 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>82</v>
@@ -12970,15 +12973,15 @@
         <v>82</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13102,10 +13105,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13231,10 +13234,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13260,13 +13263,13 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13316,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13325,7 +13328,7 @@
         <v>97</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>109</v>
@@ -13360,10 +13363,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13389,13 +13392,13 @@
         <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13424,10 +13427,10 @@
         <v>157</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -13445,7 +13448,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13489,10 +13492,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13518,13 +13521,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13574,7 +13577,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13601,7 +13604,7 @@
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -13618,10 +13621,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13745,10 +13748,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13874,10 +13877,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13903,16 +13906,16 @@
         <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13940,10 +13943,10 @@
         <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -13961,7 +13964,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13988,7 +13991,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -14005,10 +14008,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14034,16 +14037,16 @@
         <v>259</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -14071,10 +14074,10 @@
         <v>157</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -14092,7 +14095,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14119,7 +14122,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14128,7 +14131,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14136,10 +14139,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14263,10 +14266,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14392,10 +14395,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14421,16 +14424,16 @@
         <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14479,7 +14482,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14506,7 +14509,7 @@
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>82</v>
@@ -14515,7 +14518,7 @@
         <v>82</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AS91" t="s" s="2">
         <v>82</v>
@@ -14523,10 +14526,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14650,10 +14653,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14779,10 +14782,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14808,16 +14811,16 @@
         <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14827,7 +14830,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14866,7 +14869,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14893,7 +14896,7 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
@@ -14902,7 +14905,7 @@
         <v>82</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14910,10 +14913,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14939,13 +14942,13 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14995,7 +14998,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15022,7 +15025,7 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>82</v>
@@ -15031,7 +15034,7 @@
         <v>82</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
@@ -15039,10 +15042,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15068,14 +15071,14 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15124,7 +15127,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15160,7 +15163,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15168,10 +15171,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15197,14 +15200,14 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15253,7 +15256,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15280,7 +15283,7 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
@@ -15289,7 +15292,7 @@
         <v>82</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15297,10 +15300,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15323,19 +15326,19 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -15384,7 +15387,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15411,7 +15414,7 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
@@ -15420,7 +15423,7 @@
         <v>82</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15428,10 +15431,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15457,16 +15460,16 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -15515,7 +15518,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15542,7 +15545,7 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
@@ -15551,7 +15554,7 @@
         <v>82</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
@@ -15559,10 +15562,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15588,16 +15591,16 @@
         <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15610,7 +15613,7 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>82</v>
@@ -15646,7 +15649,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15673,7 +15676,7 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
@@ -15682,7 +15685,7 @@
         <v>82</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
@@ -15690,10 +15693,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15719,13 +15722,13 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15739,7 +15742,7 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>82</v>
@@ -15775,7 +15778,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15802,7 +15805,7 @@
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -15811,7 +15814,7 @@
         <v>82</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15819,10 +15822,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15845,13 +15848,13 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15902,7 +15905,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15929,7 +15932,7 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
@@ -15938,7 +15941,7 @@
         <v>82</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>82</v>
@@ -15946,10 +15949,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15975,13 +15978,13 @@
         <v>333</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16031,7 +16034,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16058,7 +16061,7 @@
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>82</v>
@@ -16067,7 +16070,7 @@
         <v>82</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>82</v>
@@ -16075,10 +16078,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16104,13 +16107,13 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16160,7 +16163,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="775">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:54:33+00:00</t>
+    <t>2026-08-06T13:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1278,10 +1278,7 @@
     <t>confidentiality</t>
   </si>
   <si>
-    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint).</t>
-  </si>
-  <si>
-    <t>En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
+    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint, ...). En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ConfidentialityClassification</t>
@@ -7858,7 +7855,7 @@
         <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>390</v>
@@ -7893,7 +7890,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7955,13 +7952,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>387</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
@@ -7986,7 +7983,7 @@
         <v>259</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>389</v>
@@ -8024,7 +8021,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -8086,10 +8083,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8115,10 +8112,10 @@
         <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -8169,7 +8166,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>97</v>
@@ -8193,10 +8190,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8213,10 +8210,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8340,10 +8337,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8469,10 +8466,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8600,10 +8597,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8626,13 +8623,13 @@
         <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8683,7 +8680,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>97</v>
@@ -8707,30 +8704,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AQ46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR46" t="s" s="2">
+      <c r="AS46" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8854,10 +8851,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8983,10 +8980,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9012,14 +9009,14 @@
         <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9032,7 +9029,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9047,28 +9044,28 @@
         <v>242</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Z49" t="s" s="2">
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9086,25 +9083,25 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -9112,10 +9109,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9141,14 +9138,14 @@
         <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9161,7 +9158,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9197,7 +9194,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9212,19 +9209,19 @@
         <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9241,10 +9238,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9267,19 +9264,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9328,7 +9325,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9355,16 +9352,16 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -9372,10 +9369,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9398,19 +9395,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9423,79 +9420,79 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="U52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF52" t="s" s="2">
+      <c r="AG52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AG52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
+      <c r="AK52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -9503,10 +9500,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9529,19 +9526,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9590,7 +9587,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9608,16 +9605,16 @@
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9634,10 +9631,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9660,19 +9657,19 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9721,7 +9718,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9739,16 +9736,16 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9765,10 +9762,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9794,14 +9791,14 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9814,43 +9811,43 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9865,19 +9862,19 @@
         <v>109</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -9894,10 +9891,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9920,17 +9917,17 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9979,7 +9976,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9994,11 +9991,11 @@
         <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
       </c>
@@ -10006,7 +10003,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -10023,10 +10020,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10052,13 +10049,13 @@
         <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10088,56 +10085,56 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AA57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="AK57" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK57" t="s" s="2">
+      <c r="AL57" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AQ57" t="s" s="2">
         <v>82</v>
       </c>
@@ -10145,15 +10142,15 @@
         <v>82</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10179,13 +10176,13 @@
         <v>341</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10235,7 +10232,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10262,7 +10259,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10279,10 +10276,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10406,10 +10403,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10535,10 +10532,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10666,10 +10663,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10692,13 +10689,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10749,7 +10746,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10767,22 +10764,22 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO62" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
@@ -10793,10 +10790,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10822,13 +10819,13 @@
         <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10857,11 +10854,11 @@
         <v>165</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10878,7 +10875,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10890,23 +10887,23 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AK63" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AK63" t="s" s="2">
+      <c r="AL63" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AO63" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10917,15 +10914,15 @@
         <v>82</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10948,13 +10945,13 @@
         <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -11005,7 +11002,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -11029,30 +11026,30 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AO64" t="s" s="2">
+      <c r="AP64" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AP64" t="s" s="2">
+      <c r="AQ64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS64" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS64" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11176,10 +11173,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11305,10 +11302,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11331,16 +11328,16 @@
         <v>98</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11390,43 +11387,43 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR67" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AS67" t="s" s="2">
         <v>82</v>
@@ -11434,10 +11431,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11460,69 +11457,69 @@
         <v>98</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q68" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="R68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
@@ -11530,34 +11527,34 @@
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AM68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>82</v>
@@ -11565,10 +11562,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11594,10 +11591,10 @@
         <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11628,56 +11625,56 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
+      <c r="AK69" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AK69" t="s" s="2">
+      <c r="AL69" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AO69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AP69" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11685,15 +11682,15 @@
         <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11719,16 +11716,16 @@
         <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11757,55 +11754,55 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AA70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AK70" t="s" s="2">
+      <c r="AL70" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>588</v>
-      </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="AP70" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11814,15 +11811,15 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11845,13 +11842,13 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11902,7 +11899,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11941,15 +11938,15 @@
         <v>82</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12073,10 +12070,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12202,10 +12199,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12231,13 +12228,13 @@
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12287,16 +12284,16 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI74" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>109</v>
@@ -12305,7 +12302,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12331,10 +12328,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12360,13 +12357,13 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12395,28 +12392,28 @@
         <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="Z75" t="s" s="2">
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12460,10 +12457,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12489,13 +12486,13 @@
         <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12545,7 +12542,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12563,16 +12560,16 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>82</v>
@@ -12589,10 +12586,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12618,13 +12615,13 @@
         <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12674,7 +12671,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12718,10 +12715,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12744,16 +12741,16 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12791,10 +12788,10 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AC78" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
@@ -12803,7 +12800,7 @@
         <v>124</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12821,39 +12818,39 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AP78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS78" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS78" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>82</v>
@@ -12875,16 +12872,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M79" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12934,7 +12931,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12952,36 +12949,36 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AM79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN79" t="s" s="2">
+      <c r="AO79" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AP79" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AP79" t="s" s="2">
+      <c r="AQ79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS79" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS79" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13105,10 +13102,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13234,10 +13231,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13263,13 +13260,13 @@
         <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13319,16 +13316,16 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>109</v>
@@ -13363,10 +13360,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13392,13 +13389,13 @@
         <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13427,28 +13424,28 @@
         <v>157</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="Z83" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13492,10 +13489,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13521,13 +13518,13 @@
         <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13577,7 +13574,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13604,7 +13601,7 @@
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -13621,10 +13618,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13748,10 +13745,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13877,10 +13874,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13906,16 +13903,16 @@
         <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -13943,28 +13940,28 @@
         <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="Z87" t="s" s="2">
+      <c r="AA87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13991,7 +13988,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -14008,10 +14005,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14037,16 +14034,16 @@
         <v>259</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -14074,28 +14071,28 @@
         <v>157</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -14122,7 +14119,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14131,7 +14128,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14139,10 +14136,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14266,10 +14263,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14395,10 +14392,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14424,16 +14421,16 @@
         <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -14482,7 +14479,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14509,16 +14506,16 @@
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AS91" t="s" s="2">
         <v>82</v>
@@ -14526,10 +14523,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14653,10 +14650,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B93" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14782,10 +14779,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14811,16 +14808,16 @@
         <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14830,46 +14827,46 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF94" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14896,16 +14893,16 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR94" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14913,10 +14910,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14942,13 +14939,13 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -14998,7 +14995,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -15025,16 +15022,16 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
@@ -15042,10 +15039,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15071,14 +15068,14 @@
         <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15127,7 +15124,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15163,7 +15160,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15171,10 +15168,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15200,14 +15197,14 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15256,7 +15253,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15283,16 +15280,16 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR97" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15300,10 +15297,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15326,19 +15323,19 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>724</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -15387,7 +15384,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15414,16 +15411,16 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR98" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>730</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15431,10 +15428,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15460,16 +15457,16 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -15518,7 +15515,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15545,16 +15542,16 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
@@ -15562,10 +15559,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15591,16 +15588,16 @@
         <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -15613,43 +15610,43 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15676,16 +15673,16 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR100" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR100" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
@@ -15693,10 +15690,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15722,13 +15719,13 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15742,43 +15739,43 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15805,16 +15802,16 @@
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR101" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15822,10 +15819,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15848,13 +15845,13 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15905,7 +15902,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15932,16 +15929,16 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR102" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="AS102" t="s" s="2">
         <v>82</v>
@@ -15949,10 +15946,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15978,13 +15975,13 @@
         <v>333</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -16034,7 +16031,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>83</v>
@@ -16061,16 +16058,16 @@
         <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR103" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR103" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="AS103" t="s" s="2">
         <v>82</v>
@@ -16078,10 +16075,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16107,13 +16104,13 @@
         <v>111</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -16163,7 +16160,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>83</v>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:55:54+00:00</t>
+    <t>2026-08-06T14:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1290,7 +1290,7 @@
     <t>visibilityStatus</t>
   </si>
   <si>
-    <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
+    <t>Statut de visibilité du document (invisible patient, invisible représentants légaux, masqué PS, etc...).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:05:46+00:00</t>
+    <t>2026-08-06T14:06:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1251,7 +1251,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (U, L, M, N, R, V) du statut de visibilité (MASQUE_PS, INVISIBLE_PATIENT, etc...) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>niveauConfidentialite : [0..*] code</t>
@@ -2780,7 +2780,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="249.46875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="255.0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:06:47+00:00</t>
+    <t>2026-08-06T14:07:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
